--- a/reportes/templates_excel/planificacion_mkt_2026_2_v1.xlsx
+++ b/reportes/templates_excel/planificacion_mkt_2026_2_v1.xlsx
@@ -7522,67 +7522,6 @@
         <a:ln>
           <a:noFill/>
         </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>847726</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>133351</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>847726</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>212560</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Imagen 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5FB54403-22C2-4ED8-8D4F-A813FDB93952}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1085851" y="133351"/>
-          <a:ext cx="3238500" cy="793584"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
